--- a/import/tb_setting1.xlsx
+++ b/import/tb_setting1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\raffle_slot\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB5A827-1DB4-4CE1-8418-7B09D1D6DE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E609D13E-B439-4609-A39B-B9C529FA8260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>id</t>
   </si>
@@ -398,7 +398,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>16</v>

--- a/import/tb_setting1.xlsx
+++ b/import/tb_setting1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\raffle_slot\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E609D13E-B439-4609-A39B-B9C529FA8260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CE1B14-FB3A-4159-BC6F-A4E4884A1B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>id</t>
   </si>
@@ -432,7 +432,7 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>22</v>
@@ -449,7 +449,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>22</v>
